--- a/temp/Report_ADMIN_03_04_5.xlsx
+++ b/temp/Report_ADMIN_03_04_5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,31 +546,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ОБЩАЯ ВЫРУЧКА:</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>400000</v>
+          <t>Садик №205</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>smetana 30%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>105000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>БЕНЗИН:</t>
+          <t>ОБЩАЯ ВЫРУЧКА:</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>505000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>БЕНЗИН:</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>ЧИСТАЯ ПРИБЫЛЬ:</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>40000</v>
+      <c r="B10" t="n">
+        <v>49000</v>
       </c>
     </row>
   </sheetData>
